--- a/output/pdf_financials_xlsx/MEX.xlsx
+++ b/output/pdf_financials_xlsx/MEX.xlsx
@@ -6240,37 +6240,37 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.401317</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.403585</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.758568</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.743013</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.215567</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.314677</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.411742</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.411742</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.411742</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.411742</v>
       </c>
     </row>
     <row r="93">
@@ -6846,16 +6846,16 @@
         <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.025267</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.006823</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.117256</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.092573</v>
       </c>
       <c r="I103" s="1" t="inlineStr">
         <is>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.098729</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.312607</v>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
@@ -7038,16 +7038,16 @@
         <v>0</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.014936</v>
+        <v>-0.040203</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.324707</v>
+        <v>-0.317884</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.203227</v>
+        <v>0.08597100000000001</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.102818</v>
+        <v>-0.010245</v>
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.108677</v>
+        <v>-0.009948</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.18091</v>
+        <v>0.493517</v>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
@@ -9877,7 +9877,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10973,7 +10977,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11361,7 +11369,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12036,7 +12048,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -13495,7 +13511,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -19705,7 +19725,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MEX.xlsx
+++ b/output/pdf_financials_xlsx/MEX.xlsx
@@ -999,31 +999,31 @@
         <v>0.733108</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2.388561</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>5.136978</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.835258</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>2.147104</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1.179158</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.948588</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>3.161154</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>3.50587</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>3.198614</v>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-2.388561</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-5.136978</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-1.835258</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-2.147104</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-1.179158</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-0.948588</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-3.161154</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-3.50587</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-3.198614</v>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.018339</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012048</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1149,25 +1149,25 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005092</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004208</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004208</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00343</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.016151</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.01096</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.003227</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -2287,25 +2287,25 @@
         <v>-5.116978</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.830898</v>
+        <v>-1.83599</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.142896</v>
+        <v>-2.147104</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.17495</v>
+        <v>-1.179158</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.9451580000000001</v>
+        <v>-0.948588</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.145003</v>
+        <v>-3.161154</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.529472</v>
+        <v>-3.540432</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.115759</v>
+        <v>-3.118986</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
         <v>-5.113043</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.817887</v>
+        <v>-1.822979</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.129483</v>
+        <v>-2.133691</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.161537</v>
+        <v>-1.165745</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.9451580000000001</v>
+        <v>-0.948588</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.145003</v>
+        <v>-3.161154</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.529472</v>
+        <v>-3.540432</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.115759</v>
+        <v>-3.118986</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>0.044377</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.834057</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.185658</v>
@@ -2793,7 +2793,7 @@
         <v>0.12146</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.09202299999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.56097</v>
@@ -2894,7 +2894,7 @@
         <v>0.044377</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.834057</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.185658</v>
@@ -2909,7 +2909,7 @@
         <v>0.12146</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.09202299999999999</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.56097</v>
@@ -3590,7 +3590,7 @@
         <v>0.017658</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.358965</v>
+        <v>0.524908</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.617826</v>
@@ -3605,7 +3605,7 @@
         <v>0.015588</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.105869</v>
+        <v>0.013846</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.09674000000000001</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -26495,7 +26495,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -32194,7 +32194,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -34921,7 +34921,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
